--- a/椙山改修/261030_第7回分科会_議事録.xlsx
+++ b/椙山改修/261030_第7回分科会_議事録.xlsx
@@ -1854,7 +1854,7 @@
       <c r="T19" s="19" t="n"/>
       <c r="U19" s="22" t="inlineStr">
         <is>
-          <t>扉本体約180kg（パネル貼り約200kg）。指挟み・寄りかかり時の安全に配慮</t>
+          <t>扉本体約180kg（木パネルと合わせて約200kg）。指挟み・寄りかかり時の安全に配慮</t>
         </is>
       </c>
       <c r="V19" s="14" t="n"/>
@@ -1898,7 +1898,7 @@
       <c r="T20" s="19" t="n"/>
       <c r="U20" s="22" t="inlineStr">
         <is>
-          <t>隙間は極力小さく、壁とのクリアランスは30→20mmで検討</t>
+          <t>隙間は極力小さく、壁とのクリアランスは20mmに決定</t>
         </is>
       </c>
       <c r="V20" s="14" t="n"/>
@@ -3343,7 +3343,7 @@
       <c r="U51" s="22" t="n"/>
       <c r="V51" s="16" t="inlineStr">
         <is>
-          <t>端部から約100〜150mm、中間は約450mmピッチを目安</t>
+          <t>端部から約100〜150mm、中間は450mmピッチ</t>
         </is>
       </c>
       <c r="W51" s="15" t="n"/>
